--- a/Framework_MWC_Testing/data/ai_processed/LoginData.xlsx
+++ b/Framework_MWC_Testing/data/ai_processed/LoginData.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,11 +456,19 @@
           <t>LG01</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ánh Dương Phạm</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này</t>
+          <t>Ánh Dương Phạm</t>
         </is>
       </c>
     </row>
@@ -470,12 +478,12 @@
           <t>LG02</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>Vui lòng điền vào trường này</t>
@@ -488,12 +496,12 @@
           <t>LG03</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>anhduong@123</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ánh Dương Phạm</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>Vui lòng điền vào trường này</t>
@@ -506,19 +514,11 @@
           <t>LG04</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Ánh Dương Phạm</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>anhduong@123</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>Vui lòng điền vào trường này</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nguyễn Văn A</t>
+          <t>anhduong@123</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -565,6 +565,698 @@
           <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
         </is>
       </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LG07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>anhduong@1234</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LG08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>anhduong@12345</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LG09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>anhduong@1234567</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LG10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>anhduong@12345678</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LG11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>anhduong@123456789</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LG12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>anhduong@1234567890</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LG13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>anhduong@12345678901</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>LG14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>anhduong@123456789012</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LG15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>anhduong@1234567890123</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LG16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>anhduong@12345678901234</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>LG17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>anhduong@123456789012345</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>LG18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>anhduong@1234567890123456</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>LG19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>anhduong@12345678901234567</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>LG20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>anhduong@123456789012345678</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>LG21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>anhduong@1234567890123456789</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>LG22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>anhduong@12345678901234567890</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>LG23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>anhduong@123456789012345678901</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LG24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>anhduong@1234567890123456789012</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>LG25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>anhduong@12345678901234567890123</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>LG26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>anhduong@123456789012345678901234</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>LG27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>anhduong@1234567890123456789012345</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>LG28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>anhduong@12345678901234567890123456</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>LG29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>anhduong@123456789012345678901234567</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>LG30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>anhduong@1234567890123456789012345678</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>LG31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>anhduong@12345678901234567890123456789</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>LG32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>anhduong@123456789012345678901234567890</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>LG33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>anhduong@1234567890123456789012345678901</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>LG34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>anhduong@12345678901234567890123456789012</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>LG35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>anhduong@123456789012345678901234567890123</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>LG36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>anhduong@1234567890123456789012345678901234</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>LG37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>anhduong@123</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>anhduong@12345678901234567890123456789012345</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>LG38</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Framework_MWC_Testing/data/ai_processed/LoginData.xlsx
+++ b/Framework_MWC_Testing/data/ai_processed/LoginData.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>AnhDuong11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>AnhDuong11</t>
         </is>
       </c>
     </row>
@@ -498,7 +498,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>AnhDuong11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -530,12 +530,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ánh Dương Phạm</t>
+          <t>AnhDuong12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>123456</t>
+          <t>anhduong@123</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>anhduong@123</t>
+          <t>AnhDuong11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>anhduong@123</t>
+          <t>anhduong@124</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -574,12 +574,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>anhduong@123</t>
+          <t>AnhDuong12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>anhduong@1234</t>
+          <t>anhduong@124</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>anhduong@123</t>
+          <t>AnhDuong12!</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>anhduong@12345</t>
+          <t>anhduong@124</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -618,12 +618,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>anhduong@123</t>
+          <t>AnhDuong12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>anhduong@1234567</t>
+          <t>anhd</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>AnhDuong123456789012345678901234567890</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>anhduong@123</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>anhduong@12345678</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>ANHDUONG123456789012345678901234567890</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>anhduong@123</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>anhduong@123456789</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -684,12 +684,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>anhduong@123</t>
+          <t>AnhDuong123456789012345678901234567890</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>anhduong@1234567890</t>
+          <t>anhduong@123!</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -706,12 +706,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>anhduong@123</t>
+          <t>   </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>anhduong@12345678901</t>
+          <t>   </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -728,12 +728,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>anhduong@123</t>
+          <t xml:space="preserve">  AnhDuong123456789012345678901234567890</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>anhduong@123456789012</t>
+          <t>   </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -750,12 +750,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>anhduong@123</t>
+          <t xml:space="preserve">AnhDuong123456789012345678901234567890   </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>anhduong@1234567890123</t>
+          <t>   </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -763,500 +763,6 @@
           <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>LG16</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>anhduong@123</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>anhduong@12345678901234</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>LG17</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>anhduong@123</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>anhduong@123456789012345</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>LG18</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>anhduong@123</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>anhduong@1234567890123456</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>LG19</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>anhduong@123</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>anhduong@12345678901234567</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>LG20</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>anhduong@123</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>anhduong@123456789012345678</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>LG21</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>anhduong@123</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>anhduong@1234567890123456789</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>LG22</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>anhduong@123</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>anhduong@12345678901234567890</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>LG23</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>anhduong@123</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>anhduong@123456789012345678901</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>LG24</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>anhduong@123</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>anhduong@1234567890123456789012</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>LG25</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>anhduong@123</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>anhduong@12345678901234567890123</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>LG26</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>anhduong@123</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>anhduong@123456789012345678901234</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>LG27</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>anhduong@123</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>anhduong@1234567890123456789012345</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>LG28</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>anhduong@123</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>anhduong@12345678901234567890123456</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>LG29</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>anhduong@123</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>anhduong@123456789012345678901234567</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>LG30</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>anhduong@123</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>anhduong@1234567890123456789012345678</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>LG31</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>anhduong@123</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>anhduong@12345678901234567890123456789</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>LG32</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>anhduong@123</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>anhduong@123456789012345678901234567890</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>LG33</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>anhduong@123</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>anhduong@1234567890123456789012345678901</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>LG34</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>anhduong@123</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>anhduong@12345678901234567890123456789012</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>LG35</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>anhduong@123</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>anhduong@123456789012345678901234567890123</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>LG36</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>anhduong@123</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>anhduong@1234567890123456789012345678901234</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>LG37</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>anhduong@123</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>anhduong@12345678901234567890123456789012345</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>LG38</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Framework_MWC_Testing/data/ai_processed/LoginData.xlsx
+++ b/Framework_MWC_Testing/data/ai_processed/LoginData.xlsx
@@ -457,7 +457,11 @@
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AnhDuong@123</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Vui lòng điền vào trường này</t>
@@ -470,12 +474,12 @@
           <t>LG02</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>AnhDuong@123</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AnhDuong11</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>Vui lòng điền vào trường này</t>
@@ -488,11 +492,7 @@
           <t>LG03</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>AnhDuong11</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
@@ -530,12 +530,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>InvalidUser</t>
+          <t>AnhDuong11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AnhDuong@123</t>
+          <t>Sai@123</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AnhDuong11</t>
+          <t>KhongDung11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>InvalidPass@123</t>
+          <t>AnhDuong@123</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -574,12 +574,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>InvalidUser</t>
+          <t>KhongDung11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>InvalidPass@123</t>
+          <t>Sai@123</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
